--- a/adobe_export.xlsx
+++ b/adobe_export.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,58 +418,177 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Capture a contemporary office space featuring sleek glass walls. Focus on the open layout that promotes collaboration and creativity with minimal distractions. Utilize soft ambient natural light streaming through large windows to illuminate the interior. Shoot using a Sony A7R IV with a 35mm lens at an aperture of f/2.8 to achieve a slight blurring of the background while keeping the foreground sharply in focus. Frame the composition from an eye-level perspective, ensuring balanced spacing between objects like modern office furniture and plants. The scene should evoke a professional yet inviting atmosphere.</v>
+        <v>A diverse group of business professionals analyzing data on a laptop in a modern office setting. The scene captures their focused expressions as they engage in discussions, illuminated by natural morning light filtering through large windows. The composition is medium-close, highlighting their interactions and the data on the screen. Shot with a Canon R5, 50mm lens at f/2.8.</v>
       </c>
       <c r="B2" t="str">
-        <v>Office Architecture with Glass Walls</v>
+        <v>Business Professionals Analyzing Data</v>
       </c>
       <c r="C2" t="str">
-        <v>office design, modern architecture, glass structure, workplace environment, urban design, interior design, business space, office layout, glass partition, architectural photography, workspace aesthetics, commercial space, light-filled office, creative workspace, modern work environment, architecture photography, contemporary office, office furniture, collaborative space, minimalist design, open plan, architecture details, glass offices, workspace inspiration, bright office space, design elements, buildings, interior architecture, contemporary design, workspace productivity, professional environment, office interiors, workspace layout, interior spaces, creative office, elegant workplace, transparent walls, office building, natural light, efficient workspace, architectural spaces, colorful office, artistic office, peaceful workspace, office views</v>
+        <v>business professionals, analyzing data, team collaboration, strategic planning, office environment, realistic setting, emotional engagement, focused expressions, natural lighting, high-resolution, professional attire, diverse team, laptop, data chart, collaboration tools, team meeting, brainstorming session, creative ideas, determination, success, problem-solving, work motivation, interpersonal skills, business strategy, goal-oriented, analytical mindset, professional development, communication, display screen, decision making, engaged team, empathetic communication, planning session, confidence, team dynamics, work environment, inspiration, enthusiasm</v>
       </c>
       <c r="D2" t="str">
-        <v>An architectural depiction of a modern office featuring glass walls that create an open and bright workspace.</v>
+        <v>A focused group of business professionals engaged in a meeting, analyzing data displayed on a laptop screen in a modern, well-lit office environment. The emotional tone reflects determination and teamwork.</v>
       </c>
       <c r="E2" t="str">
-        <v>Buildings and Architecture</v>
+        <v>Business</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Photograph a bright and spacious open-plan office characterized by its stylish glass partitions. Capture the essence of a modern workspace where collaborative efforts thrive, bathed in natural light flowing through large windows. Use a Canon EOS R5 paired with an 85mm lens set to f/1.8, creating a shallow depth of field to emphasize the front elements while softening the background. Position the camera for a close-up shot that highlights both the interior design and workspace setup. The arrangement should be intentional, showcasing modern furniture and decor that reflect a productive workplace atmosphere.</v>
+        <v>An entrepreneur enthusiastically presenting ideas to a small team in a bright office, using a whiteboard covered with sketches. Their excited expression reflects confidence and creativity. Shot in natural light, the medium shot captures the full scene with focus on interactions. Captured with a Sony A7R IV, 35mm lens at f/4.</v>
       </c>
       <c r="B3" t="str">
-        <v>Open Plan Office with Glass Walls</v>
+        <v>Entrepreneur Presenting Innovative Ideas</v>
       </c>
       <c r="C3" t="str">
-        <v>workspace design, modern office, architecture, glass office, business architecture, workspace layout, office windows, contemporary interiors, minimalist office, natural light, collaborative workspace, business environment, interior architecture, workspace aesthetics, interior design, urban workspace, office building design, architectural photography, bright workspace, professional space, creative environment, efficient layout, workspace inspiration, open office layout, glass partitioning, interior design elements, workspace productivity, business space, modern architecture, architecture details, clean office space, office interiors, workspace features, elegant workspace, transparent design, architectural view, colorful office, artistic workspace, professional environment, office aesthetics, architectural spaces, interior design concepts</v>
+        <v>entrepreneur, presenting ideas, innovation, pitch presentation, bright office, excited expression, creative thinking, collaborative atmosphere, whiteboard, sketching ideas, team feedback, problem-solving, engaging conversation, clear communication, motivating environment, natural light, sharp focus, professional attire, diversity, business proposal, inspiring discussion, team brainstorming, work success, initiative, confidence, creativity, entrepreneurship, startup culture, actionable insights, feedback exchange, strategy meeting, positive energy, business collaboration, visual presentation, hands-on approach, involvement, leadership, engagement, effective communication, energetic atmosphere</v>
       </c>
       <c r="D3" t="str">
-        <v>Illustrate an open-plan office showcasing stylish glass walls that enhance the workspace's modern appeal.</v>
+        <v>An entrepreneur passionately presenting innovative ideas to a group of attentive colleagues in a bright office setting, surrounded by creative visuals on a whiteboard. The scene evokes excitement and collaboration.</v>
       </c>
       <c r="E3" t="str">
-        <v>Buildings and Architecture</v>
+        <v>Business</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Visualize a modern workspace equipped with expansive glass walls that create a seamless blend of the interior and exterior. Use natural light pouring in to illuminate the space, showcasing its artistic design. The scene should be shot with a Nikon Z9 paired with a 50mm lens set at f/2.8 to ensure a sharp focus on the aesthetics while maintaining a gently blurred background. Opt for a top-down composition that balances the layout of the office furniture with clear negative space around it. This curated environment must convey a blend of professionalism and creativity, enticing the viewer into the world of modern business.</v>
+        <v>A diverse team celebrating the successful completion of a project in a modern office space. The scene shows joyful expressions with members engaging in high-fives and laughter, illuminated with natural light streaming through large windows. Captured as a wide angle to include the entire group dynamics, using a Canon R5, 24mm lens at f/3.5.</v>
       </c>
       <c r="B4" t="str">
-        <v>Modern Workspace Design with Glass Walls</v>
+        <v>Team Celebrating Successful Project Completion</v>
       </c>
       <c r="C4" t="str">
-        <v>contemporary office, workspace aesthetics, business architecture, office design, glass offices, minimalist interiors, interior photography, bright workspace, urban design, collaborative environment, interior elements, architectural photography, office creativity, professional design, space layout, workspace inspiration, business space, natural light, interior design, efficient workspace, modern design, collaborative office, interior space, architecture, office interiors, open space, glass structure, workspace features, commercial environment, professional aesthetics, light-filled office, architecture details, elegant workspace, artistic office design, office furniture, transparent walls, office productivity, creative design, workspace environment, office layout, workplace aesthetics, elegant design, architectural view, office charm</v>
+        <v>team celebration, successful project, achievement, joyful expressions, modern office, team unity, high-five, celebratory atmosphere, office party, group positivity, motivational environment, shared success, team spirit, natural light, bonding experience, collective effort, engaging moment, joyful teamwork, sign of success, excitement, camaraderie, professional setting, dynamic interaction, smiling faces, win celebration, business success, positive reinforcement, goal achievement, enthusiasm, high-energy, group dynamics, networking, business growth, achievements recognized, motivating others, encouragement, reflecting values, connections, celebration of achievements, reaching milestones</v>
       </c>
       <c r="D4" t="str">
-        <v>Capture the essence of a modern workspace featuring expansive glass walls that enhance architectural beauty.</v>
+        <v>A team in a modern office joyfully celebrating the successful completion of a project, expressed through high-fives and smiling faces. The emotional tone highlights collective achievement and unity.</v>
       </c>
       <c r="E4" t="str">
-        <v>Buildings and Architecture</v>
+        <v>Business</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>A manager engaged in a thoughtful performance review with an employee in a calm, well-lit office space. The scene captures sincere communication, highlighting the thoughtful expressions of both individuals. Shot with a Sony A7R IV, 50mm lens at f/2.0, in a medium framing to emphasize their interaction.</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Manager Conducting Performance Review</v>
+      </c>
+      <c r="C5" t="str">
+        <v>manager, performance review, constructive feedback, professional setting, calm office, thoughtful expressions, goal setting, improvement discussions, clarity, communication skills, focus, progress tracking, workspace dynamics, personal growth, confidentiality, individual feedback, business leadership, natural light, Office interaction, balanced composition, sharp focus, empathy, work relationship, professional guidance, development opportunities, feedback sessions, strategic thinking, work objectives, motivation, planning, performance assessment, positive results, workplace support, enhancing skills, eagerness to improve, respectful dialogue, insightful conversation, professional connection, team development, career progress</v>
+      </c>
+      <c r="D5" t="str">
+        <v>A manager calmly conducting a performance review with an employee in a serene office environment, encapsulating thoughtful discussions about personal growth and constructive feedback through focused expressions.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Business</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>A team of visionaries brainstorming ideas in an inspirational office filled with natural light. Each member is actively engaged in discussion while sketching their concepts on notepads, creating a dynamic exchange of ideas. The composition is wide to capture their enthusiasm, shot with a Canon R5, 24mm lens at f/4.</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Innovative Visionaries Brainstorming Ideas</v>
+      </c>
+      <c r="C6" t="str">
+        <v>visionaries, brainstorming ideas, creative session, collaborative environment, inspirational setting, eager expressions, dynamic exchange, team brainstorming, office atmosphere, natural lighting, engaged conversation, sketching concepts, creative flow, motivated team, problem-solving mindset, strategic workshop, diverse perspectives, ideas generation, sharp focus, present ideas, drafting proposals, vision planning, collaboration tools, thought sharing, innovative thinking, team dynamics, energy flow, business vision, meeting of minds, optimism, active participation, goal alignment, engagement, positive vibes, optimal creativity, productive discussions, team synergy, office creatives, success mindset</v>
+      </c>
+      <c r="D6" t="str">
+        <v>A group of innovative visionaries engaged in a vibrant brainstorming session, exchanging ideas and sketching concepts on a notepad in an inspirational office environment. The scene reflects creativity and teamwork.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Business</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>A Vietnamese woman walking through a bustling market, wearing traditional attire. The scene is filled with colorful stalls, showcasing local produce and street vendors. The environment is lively, representing everyday life in Vietnam. The lighting is natural and warm, illuminating her joyful expression as she interacts with the bustling crowd. Shot with a Canon R5, 50mm lens, f/2.8, in a dynamic composition that captures the energy and culture of the city.</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Vietnamese Woman Walking Through Bustling Market</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Vietnamese woman, market, bustling environment, street photography, lifestyle, colorful stalls, natural lighting, traditional attire, local produce, dynamic movement, urban landscape, cultural richness, everyday life, human connection, vibrant colors, authentic experience, photorealistic, documentary style, city life, local vendors, street hustle, cultural immersion, motion blur, happy expression, community interaction, crowded market, contrast, depth of field, engagement, candid photography, food stalls, cultural authenticity, trendy lifestyle, rich textures, dynamic composition, neighborhood vibe, daily routine, warm tones, zest for life, immersive atmosphere</v>
+      </c>
+      <c r="D7" t="str">
+        <v>A Vietnamese woman dressed in traditional attire walks gracefully through a vibrant market filled with local vendors and colorful produce, capturing the essence of urban lifestyle and culture.</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Landscapes</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>A group of local fishermen casting their nets into the ocean at sunrise. The scene reflects tranquility, with golden light softly illuminating the water. The fishermen are mid-action, showcasing the traditional methods of fishing. Shot from a distance with a Sony A7R IV using a 24-70mm lens at f/4. The composition captures the serenity of the early morning and the cultural heritage of Vietnam’s seaside communities.</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Local Fishermen Casting Nets at Sunrise</v>
+      </c>
+      <c r="C8" t="str">
+        <v>fisherman, sunrise, tranquil environment, Vietnam coastline, casting nets, morning light, silhouette, nature, fishing boat, serenity, ocean waves, sun reflections, local lifestyle, peaceful, crew members, traditional fishing, daily routine, candid moment, cultural heritage, photorealistic, documentary style, calm waters, fishing nets, golden hour, vivid colors, immersive atmosphere, natural scenery, rural life, community bonding, early morning, working class, local traditions, blue tones, soft shadows, persistence, deep connection, capturing motion, tranquil experience</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Local fishermen casting nets into the water at sunrise, surrounded by calm ocean waves and mist, embodying the serene beauty of Vietnam’s coastal lifestyle.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Landscapes</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Young artists collaboratively painting vibrant murals on a street wall. The environment showcases a dynamic urban setting filled with color and creativity. Natural light falls onto the scene, highlighting their focused expressions as they engage passionately with their art. Captured with a Canon R5 camera, 35mm lens, at f/2. The composition emphasizes the collaboration and cultural impact of public art in a lively community setting.</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Young Artists Painting Murals on Street Walls</v>
+      </c>
+      <c r="C9" t="str">
+        <v>young artists, mural painting, creative environment, urban street, collaborative effort, vibrant colors, artistic expression, cultural relevance, community art, documentary style, public spaces, youth culture, graffiti, local neighborhood, mural project, inspiring creativity, colorful artwork, natural light, dynamic motion, hands-on activity, advertising for passion, artists at work, close collaboration, urban lifestyle, candid photography, innovative art, vibrancy, community bonding, textured walls, artistic tools, engagement, youth initiative, cultural dialogue, expressive art, neighborhood revitalization, collaboration, shared vision</v>
+      </c>
+      <c r="D9" t="str">
+        <v>A group of young artists energetically paints colorful murals on street walls, contributing to the cultural vibrancy and creative landscape of their urban neighborhood in Vietnam.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Landscapes</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>An elderly man animatedly sharing stories at a local café, seated comfortably with smiling companions. The intimate setting is enriched with natural light, emphasizing the warm atmosphere and connections between patrons. Shot with a Sony A7R IV using a 50mm lens at f/1.8, the composition captures candid moments of joy and cultural exchange in a charming neighborhood venue.</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Elderly Man Sharing Stories at Local Café</v>
+      </c>
+      <c r="C10" t="str">
+        <v>elderly man, storytelling, local café, intimate environment, warm atmosphere, cultural exchange, community engagement, rich history, photorealistic, documentary style, sociability, traditional establishment, friendly interaction, candid photography, human connection, natural light, expressive gestures, i-contextual moments, community stories, cultural legacy, table setting, coffee cups, immersive experience, soft focus, endearing expressions, local culture, wholesome atmosphere, neighborhood charm, historical context, delightful conversation, aged wisdom, smiling faces, warm colors, relaxed vibe</v>
+      </c>
+      <c r="D10" t="str">
+        <v>An elderly man shares captivating stories with friends at a local café, fostering a sense of community in the warm and inviting atmosphere.</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Landscapes</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>A couple riding a scooter through the scenic countryside, showcasing the adventure and joy of travel. The environment is lush and vibrant, with rolling hills and open skies all around. The scene is bathed in natural light, creating a sense of warmth and freedom. Shot with a Canon R5, 24mm lens at f/4. The composition highlights the connection between the couple and the surrounding beauty of Vietnam’s nature.</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Couple Riding a Scooter Through Scenic Countryside</v>
+      </c>
+      <c r="C11" t="str">
+        <v>couple, scooter, countryside, adventurous spirit, natural scenery, road trip, freedom, lush greenery, Vietnam landscape, joyful expression, intimate bond, dynamic movement, open road, sunny day, photorealistic, documentary style, happy moments, candid photography, travel lifestyle, exploration, tropical environment, cultural connection, sky background, road curves, lifestyle photography, emotional connection, adventure, vivid colors, shared experience, local culture, charming landscape, comfort, candid humor, speed, pageantry, natural light, sensation of freedom</v>
+      </c>
+      <c r="D11" t="str">
+        <v>A couple joyfully rides a scooter through the picturesque Vietnamese countryside, embodying a sense of freedom and adventure amid lush landscapes.</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Landscapes</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/adobe_export.xlsx
+++ b/adobe_export.xlsx
@@ -418,172 +418,172 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>A diverse group of business professionals analyzing data on a laptop in a modern office setting. The scene captures their focused expressions as they engage in discussions, illuminated by natural morning light filtering through large windows. The composition is medium-close, highlighting their interactions and the data on the screen. Shot with a Canon R5, 50mm lens at f/2.8.</v>
+        <v>The camera captures an intimate scene inside a Vietnamese home kitchen at eye-level, providing a documentary-style perspective of a daily coffee ritual. The composition follows the rule of thirds, with the coffee brewing setup slightly off-center, creating a natural asymmetry. A soft, warm light filters through a nearby window, enveloping the scene in a golden hue, typical of early morning. The focus prioritizes the interaction between human hands and the drip coffee setup, with the intricate textures of the coffee grounds and glassware sharply defined. The background captures the subtle chaos of a lived-in kitchen, with gently tangled cables and steaming pots layered in the frame. Light steam creates a thin, ambient haze that diffuses the background details, adding atmospheric depth. The slight handheld imperfection in framing offers a candid and observational feel, capturing the essence of a lived moment in a Vietnamese household. This scene feels like a cherished memory, both visually immersive and emotionally authentic, perfectly aligned with premium commercial standards.</v>
       </c>
       <c r="B2" t="str">
-        <v>Business Professionals Analyzing Data</v>
+        <v>Vietnamese Home Coffee Ritual</v>
       </c>
       <c r="C2" t="str">
-        <v>business professionals, analyzing data, team collaboration, strategic planning, office environment, realistic setting, emotional engagement, focused expressions, natural lighting, high-resolution, professional attire, diverse team, laptop, data chart, collaboration tools, team meeting, brainstorming session, creative ideas, determination, success, problem-solving, work motivation, interpersonal skills, business strategy, goal-oriented, analytical mindset, professional development, communication, display screen, decision making, engaged team, empathetic communication, planning session, confidence, team dynamics, work environment, inspiration, enthusiasm</v>
+        <v>vietnam coffee, vietnamese coffee, drip coffee, home kitchen, daily life, vietnam lifestyle, cultural tradition, coffee brewing, vietnamese culture, aromatic coffee, candid moment, home ritual, morning routine, authentic interaction, intimate setting, warm ambiance, natural lighting, golden hour, storytelling photography, organic textures, lived-in space, realistic environment, emotional depth, documentary realism, human connection, cultural experience, environmental storytelling, unposed scene, daily ritual, vietnamese home, optical realism, textured surfaces, imperfect symmetry, natural posture, unplanned moment, commercially valuable, naturally captured, cozy atmosphere, visual immersion, captured experience, authentic expression, natural interaction, warm tones, morning light, documentary style, local tradition</v>
       </c>
       <c r="D2" t="str">
-        <v>A focused group of business professionals engaged in a meeting, analyzing data displayed on a laptop screen in a modern, well-lit office environment. The emotional tone reflects determination and teamwork.</v>
+        <v>A naturally captured moment of a Vietnamese home coffee ritual, showcasing the authentic and immersive experience of preparing drip coffee in a warm and intimate home kitchen setting. The scene reflects daily life in Vietnam, with cultural traditions highlighted through storytelling photography.</v>
       </c>
       <c r="E2" t="str">
-        <v>Business</v>
+        <v>Lifestyle</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>An entrepreneur enthusiastically presenting ideas to a small team in a bright office, using a whiteboard covered with sketches. Their excited expression reflects confidence and creativity. Shot in natural light, the medium shot captures the full scene with focus on interactions. Captured with a Sony A7R IV, 35mm lens at f/4.</v>
+        <v>Capture a street-level perspective on a bustling Vietnamese street during the rainy season, where a multitude of scooters weave through traffic. The camera sits at eye-level, observing the controlled chaos of the morning commute. A wide-angle lens is utilized to encompass the layered depth of the scene, from the glistening wet pavement in the foreground to the blurred outlines of city life in the background. The focus is razor sharp on a group of commuters in motion, their expressions partially obscured by rain gear as they navigate the slick streets. Traffic lights cast a soft glow, reflected in the shallow puddles that dot the road, adding dimension to the environment. Raindrops gently distort the scene, creating a natural diffusion of light while humidity hangs in the air, visible in the slight blur of distant neon signs. The framing is intentionally imperfect, with elements of daily street life partially obstructing the view, conveying the authentic hustle of an urban Vietnamese commute.</v>
       </c>
       <c r="B3" t="str">
-        <v>Entrepreneur Presenting Innovative Ideas</v>
+        <v>Vietnamese Rainy Scooter Commute</v>
       </c>
       <c r="C3" t="str">
-        <v>entrepreneur, presenting ideas, innovation, pitch presentation, bright office, excited expression, creative thinking, collaborative atmosphere, whiteboard, sketching ideas, team feedback, problem-solving, engaging conversation, clear communication, motivating environment, natural light, sharp focus, professional attire, diversity, business proposal, inspiring discussion, team brainstorming, work success, initiative, confidence, creativity, entrepreneurship, startup culture, actionable insights, feedback exchange, strategy meeting, positive energy, business collaboration, visual presentation, hands-on approach, involvement, leadership, engagement, effective communication, energetic atmosphere</v>
+        <v>vietnam street, scooter commute, rainy season, urban vietnam, southeast asia traffic, motorbike, rainy day, vietnamese culture, street scene, daily life, authentic moment, urban lifestyle, traffic congestion, wet pavement, city environment, candid shot, realistic photography, documentary style, human interaction, commute experience, raindrop texture, motion blur, natural lighting, reflective surface, street vendor, asian traffic, urban hustle, weather interaction, environmental detail, cultural scene, city life, southeast asian city, people on scooters, street hustle, urban realism, natural framing, dynamic perspective, documentary realism, intimate perspective, localized culture, cityscape, authentic emotion, lived-in environment, communal activity, street photography, commercially licensable, professional capture</v>
       </c>
       <c r="D3" t="str">
-        <v>An entrepreneur passionately presenting innovative ideas to a group of attentive colleagues in a bright office setting, surrounded by creative visuals on a whiteboard. The scene evokes excitement and collaboration.</v>
+        <v>A bustling Vietnamese street during the rainy season, capturing a candid moment of scooter commuters navigating wet city roads. The image showcases Southeast Asian traffic culture, focusing on the dynamic interaction between people and their urban environment. Raindrops create natural reflections on the pavement, enhancing the authentic atmosphere of daily life in urban Vietnam.</v>
       </c>
       <c r="E3" t="str">
-        <v>Business</v>
+        <v>Lifestyle</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>A diverse team celebrating the successful completion of a project in a modern office space. The scene shows joyful expressions with members engaging in high-fives and laughter, illuminated with natural light streaming through large windows. Captured as a wide angle to include the entire group dynamics, using a Canon R5, 24mm lens at f/3.5.</v>
+        <v>Capture an intimate, eye-level perspective of a bustling Vietnamese tailor workshop, where an artisan works meticulously at a sewing machine, surrounded by an array of colorful fabrics and traditional tools. The camera angle should slightly favor a three-quarter view, allowing a glimpse of the workshop's layered depth and lived-in authenticity. Use a focal length that naturally separates the subject from the background without isolating them, maintaining sharp focus on the tailor's hands and the sewing machine, while the workshop’s ambient details fade softly into a natural bokeh. The composition adheres to the rule of thirds, with the tailor positioned slightly off-center, immersed in their task, providing a candid, observational feel. The lighting should mimic a warm, soft daylight streaming through an unseen window, creating natural highlights and gentle shadows that add depth to the scene. Include subtle atmospheric elements such as dust particles catching the light and fabric edges fluttering, enhancing the tactile realism. The workshop's textured imperfections, like wooden tables with nicks and aging cloth patterns, should convey a sense of history and continuity. This frame should evoke the essence of cultural craftsmanship and human dedication, captured with commercial-grade technical precision and storytelling depth.</v>
       </c>
       <c r="B4" t="str">
-        <v>Team Celebrating Successful Project Completion</v>
+        <v>Vietnamese Tailor Workshop</v>
       </c>
       <c r="C4" t="str">
-        <v>team celebration, successful project, achievement, joyful expressions, modern office, team unity, high-five, celebratory atmosphere, office party, group positivity, motivational environment, shared success, team spirit, natural light, bonding experience, collective effort, engaging moment, joyful teamwork, sign of success, excitement, camaraderie, professional setting, dynamic interaction, smiling faces, win celebration, business success, positive reinforcement, goal achievement, enthusiasm, high-energy, group dynamics, networking, business growth, achievements recognized, motivating others, encouragement, reflecting values, connections, celebration of achievements, reaching milestones</v>
+        <v>vietnam tailor, sewing workshop, craftsmanship, vietnam textile, local business, traditional tailoring, artisan at work, needle and thread, fabric cutting, tailoring tools, sewing machine, handmade clothing, urban culture, textile industry, asian craftsmanship, vietnam culture, hands-on work, tailor's workspace, garment making, fine textiles, workshop lighting, documentary style, everyday life, local tradition, craftsmanship pride, vietnamese lifestyle, skilled hands, authentic environment, warm tones, realistic lighting, candid moment, community business, workshop atmosphere, cultural heritage, art of tailoring, craftsman focus, artisanal details, fabric textures, working process, neighborhood life, non-posed scene, professional photography, commercial relevance, emotional depth, heritage preservation, intimate framing, storytelling composition, human connection</v>
       </c>
       <c r="D4" t="str">
-        <v>A team in a modern office joyfully celebrating the successful completion of a project, expressed through high-fives and smiling faces. The emotional tone highlights collective achievement and unity.</v>
+        <v>A candid moment capturing the authentic environment of a local Vietnamese tailor workshop, where a skilled artisan is deeply engaged in crafting garments. The scene is filled with the natural ambience of a traditional sewing workspace, rich with texture and warmth. The tailor, absorbed in precise fabric cutting and sewing, is framed in a way that showcases both the craftsmanship and the cultural heritage of Vietnam. The lighting is realistically soft, reminiscent of natural window light, which highlights the intricate details of the fabric and tools scattered around. This image encapsulates the essence of everyday life and the pride of local craftsmanship, making it suitable for commercial licensing with its genuine depiction of cultural and emotional storytelling.</v>
       </c>
       <c r="E4" t="str">
-        <v>Business</v>
+        <v>Lifestyle</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>A manager engaged in a thoughtful performance review with an employee in a calm, well-lit office space. The scene captures sincere communication, highlighting the thoughtful expressions of both individuals. Shot with a Sony A7R IV, 50mm lens at f/2.0, in a medium framing to emphasize their interaction.</v>
+        <v>Photograph from eye-level, capturing a Vietnamese family gathered around a worn wooden dining table in a cozy, lived-in home. The camera focuses on the family, engaging in warm conversation and laughter as they share an array of traditional homemade Vietnamese dishes. The composition follows the rule of thirds, gently leading the eye from a grandmother serving a steaming bowl of pho to the eager expressions of grandchildren anticipating their meal. The scene is bathed in soft, natural golden-hour light filtering through partially drawn curtains, casting subtle, warm shadows across the room. This creates a subtle interplay of highlights and shadows, emphasizing the comforting domestic textures, from the smooth porcelain of the bowls to the rustic wooden table surface. The slightly elevated angle allows for a layered foreground of scattered chopsticks and porcelain bowls, while family members, with natural posture variations, form the midground. In the background, kitchen appliances and faded family photos are softly blurred, enhancing the familial atmosphere without distracting from the central narrative. The image embodies the essence of documentary realism, capturing the nuanced emotion and everyday beauty of an authentic Vietnamese family dining experience, creating a commercially valuable and culturally rich moment perfectly suited for Adobe Stock.</v>
       </c>
       <c r="B5" t="str">
-        <v>Manager Conducting Performance Review</v>
+        <v>Vietnamese Family Dinner at Home</v>
       </c>
       <c r="C5" t="str">
-        <v>manager, performance review, constructive feedback, professional setting, calm office, thoughtful expressions, goal setting, improvement discussions, clarity, communication skills, focus, progress tracking, workspace dynamics, personal growth, confidentiality, individual feedback, business leadership, natural light, Office interaction, balanced composition, sharp focus, empathy, work relationship, professional guidance, development opportunities, feedback sessions, strategic thinking, work objectives, motivation, planning, performance assessment, positive results, workplace support, enhancing skills, eagerness to improve, respectful dialogue, insightful conversation, professional connection, team development, career progress</v>
+        <v>vietnam family, vietnam dinner, home cooking, asian family meal, domestic life, traditional cuisine, family gathering, cultural tradition, homemade food, authentic vietnamese, generational connection, shared meal, kitchen table, warm lighting, natural interaction, candid moment, documentary style, emotional authenticity, immersive storytelling, social bonding, meal preparation, culinary heritage, intimate atmosphere, domestic setting, real life scene, domestic warmth, food and culture, lifestyle photography, asian family culture, community sharing, culinary experience, emotional connection, cultural identity, home interior, family dynamic, generational tradition, kitchen ambiance, lived experience, visual storytelling, cultural meal, domestic realism, warm tones, ethnic diversity, family tradition, candid family interaction, cultural representation, home dining</v>
       </c>
       <c r="D5" t="str">
-        <v>A manager calmly conducting a performance review with an employee in a serene office environment, encapsulating thoughtful discussions about personal growth and constructive feedback through focused expressions.</v>
+        <v>Capture an intimate Vietnamese family dinner scene in a home setting, showcasing the authentic warmth and shared connections of an Asian family meal. Emphasize natural interaction, emotional depth, and cultural authenticity within a welcoming domestic environment.</v>
       </c>
       <c r="E5" t="str">
-        <v>Business</v>
+        <v>Lifestyle</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>A team of visionaries brainstorming ideas in an inspirational office filled with natural light. Each member is actively engaged in discussion while sketching their concepts on notepads, creating a dynamic exchange of ideas. The composition is wide to capture their enthusiasm, shot with a Canon R5, 24mm lens at f/4.</v>
+        <v>Capture a candid, observational scene from a Vietnamese apartment balcony, where colorful laundry hangs on lines amidst a densely-packed urban environment. The camera should be positioned at a natural eye-level, providing a slightly off-centered, intimate view of the balcony's daily life and vibrant, weathered textures. Employ a medium focal length to naturally separate the foreground laundry from the cluttered background, enhancing the documentary realism. The composition should include subtle imperfections, such as slight motion in the fabric and uneven framing through passing pedestrians, contributing to the lived-in atmosphere. Soft, diffused lighting from an overcast sky interacts with the surfaces, highlighting the authentic textures and colors of the clothes in contrast to the grayish tone of the building's facade. Focus on capturing the layered depth of the environment, where the bustling urban life is subtly visible in the distance through partially obstructed views. This image should depict a moment that feels both visually immersive and emotionally relatable, transporting the viewer to a typical scene of balcony life in Southeast Asia.</v>
       </c>
       <c r="B6" t="str">
-        <v>Innovative Visionaries Brainstorming Ideas</v>
+        <v>Vietnamese Laundry Balcony Scene</v>
       </c>
       <c r="C6" t="str">
-        <v>visionaries, brainstorming ideas, creative session, collaborative environment, inspirational setting, eager expressions, dynamic exchange, team brainstorming, office atmosphere, natural lighting, engaged conversation, sketching concepts, creative flow, motivated team, problem-solving mindset, strategic workshop, diverse perspectives, ideas generation, sharp focus, present ideas, drafting proposals, vision planning, collaboration tools, thought sharing, innovative thinking, team dynamics, energy flow, business vision, meeting of minds, optimism, active participation, goal alignment, engagement, positive vibes, optimal creativity, productive discussions, team synergy, office creatives, success mindset</v>
+        <v>vietnam apartment, urban laundry, balcony life, daily routine, southeast asia housing, crowded balcony, hanging clothes, city life, domestic scene, dense urban environment, local lifestyle, cultural environment, realistic photography, natural framing, candid interaction, human presence, textured surfaces, weathered materials, intimate perspective, vibrant colors, documentary realism, observational photography, warm atmosphere, tactile textures, genuine emotion, street sounds, historical architecture, neighborhood view, overcast lighting, window reflections, fabric movement, casual life, authentic experience, everyday activity, community interaction, environmental texture, spatial realism, human connection, cultural representation, geographical authenticity, visually immersive, emotionally relatable, natural motion, true moment, professional-grade detail, commercial potential, urban routine, asymmetrical composition</v>
       </c>
       <c r="D6" t="str">
-        <v>A group of innovative visionaries engaged in a vibrant brainstorming session, exchanging ideas and sketching concepts on a notepad in an inspirational office environment. The scene reflects creativity and teamwork.</v>
+        <v>A candidly captured scene of a Vietnamese apartment balcony bustling with daily life as colorful clothes hang out to dry. This intimate portrayal involves environmental textures that highlight the dense urban setting common in Southeast Asia. The shot captures a moment of genuine human interaction, emphasizing the cultural landscape of Vietnam's city housing.</v>
       </c>
       <c r="E6" t="str">
-        <v>Business</v>
+        <v>Lifestyle</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>A Vietnamese woman walking through a bustling market, wearing traditional attire. The scene is filled with colorful stalls, showcasing local produce and street vendors. The environment is lively, representing everyday life in Vietnam. The lighting is natural and warm, illuminating her joyful expression as she interacts with the bustling crowd. Shot with a Canon R5, 50mm lens, f/2.8, in a dynamic composition that captures the energy and culture of the city.</v>
+        <v>The camera captures a bustling Vietnamese street food stall from an eye-level viewpoint, subtly framed by passing pedestrians. The lens focuses on a local vendor passionately preparing noodles, surrounded by vibrant market activity. The environment is rich with layered depth, featuring hanging lanterns and colorful produce stalls in the background. The vendor’s hands move skillfully, tossing fresh ingredients in a sizzling pan, exuding an aroma almost palpable through the image. Warm, natural light filters through the market canopy, creating a cozy, authentic ambiance. The scene is filled with atmospheric details—condensation clings to metal surfaces, and the air is humid with culinary steam. The photograph is candid, capturing a true slice of life, with vendors and customers interacting naturally amid the lively market. Textures are tactile, from the worn fabric of the vendor’s apron to the rough, weathered wood of the noodle stall. The overall composition is asymmetrical, capturing the essence of a bustling, yet intimate marketplace, where each moment tells a part of the vibrant story of Vietnamese street food culture.</v>
       </c>
       <c r="B7" t="str">
-        <v>Vietnamese Woman Walking Through Bustling Market</v>
+        <v>Vietnamese Street Food Preparation</v>
       </c>
       <c r="C7" t="str">
-        <v>Vietnamese woman, market, bustling environment, street photography, lifestyle, colorful stalls, natural lighting, traditional attire, local produce, dynamic movement, urban landscape, cultural richness, everyday life, human connection, vibrant colors, authentic experience, photorealistic, documentary style, city life, local vendors, street hustle, cultural immersion, motion blur, happy expression, community interaction, crowded market, contrast, depth of field, engagement, candid photography, food stalls, cultural authenticity, trendy lifestyle, rich textures, dynamic composition, neighborhood vibe, daily routine, warm tones, zest for life, immersive atmosphere</v>
+        <v>vietnam street food, noodle vendor, food preparation, local cuisine, vietnam cooking, street vendor, daily life, asian market, traditional recipes, culinary skills, authentic flavors, chef at work, fresh ingredients, noodle booth, sizzling pan, busy marketplace, cultural heritage, urban street, vendor interaction, local experience, vibrant atmosphere, handmade noodles, street food stall, culinary tradition, food authenticity, dynamic scene, natural environment, spontaneous moment, immersive photograph, candid capture, documentary photography, cultural exploration, crowded market, everyday activity, human connection, realistic lighting, natural textures, textured background, community spirit, warm ambiance, bustling street, food culture, handcrafted meals, local vendors, flavorful dishes, rich storytelling</v>
       </c>
       <c r="D7" t="str">
-        <v>A Vietnamese woman dressed in traditional attire walks gracefully through a vibrant market filled with local vendors and colorful produce, capturing the essence of urban lifestyle and culture.</v>
+        <v>A vibrant scene capturing the dynamic and authentic atmosphere of a Vietnamese street food market. The image showcases a noodle vendor energetically preparing local cuisine amid a bustling marketplace. The environment feels alive with the sizzling sounds and aromatic scents of traditional cooking, emphasizing the cultural significance of street food in daily Vietnamese life.</v>
       </c>
       <c r="E7" t="str">
-        <v>Landscapes</v>
+        <v>Lifestyle</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>A group of local fishermen casting their nets into the ocean at sunrise. The scene reflects tranquility, with golden light softly illuminating the water. The fishermen are mid-action, showcasing the traditional methods of fishing. Shot from a distance with a Sony A7R IV using a 24-70mm lens at f/4. The composition captures the serenity of the early morning and the cultural heritage of Vietnam’s seaside communities.</v>
+        <v>The camera captures a Vietnamese student deeply focused on studying late at night in a modest urban apartment. The angle is slightly above eye level, and the camera height is just above the student's head, creating an intimate, observational feel. A wide lens subtly softens the background, emphasizing layered depth as stacks of books frame the foreground. The student's desk is cluttered yet organized, with scattered notebooks and a warm desk lamp illuminating the workspace in a soft, cozy glow. Subjects in focus include the student's pensive expression and their attentive hands turning a page. The environment feels naturally lived-in, with signs of daily life like a wrinkled jacket draped over a chair and a half-open window allowing in a whisper of city noise. The lighting gently casts shadows that stretch across the wooden floor, adding texture and storytelling depth. There's an authentic humidity in the air, lightly blurring the distant city lights visible through the window, enhancing the late-night ambiance. This captured frame is a testament to the student's dedication, presented with raw documentary realism and emotional authenticity, ready for commercial licensing without any visual artifacts.</v>
       </c>
       <c r="B8" t="str">
-        <v>Local Fishermen Casting Nets at Sunrise</v>
+        <v>Vietnamese Student Studying Late</v>
       </c>
       <c r="C8" t="str">
-        <v>fisherman, sunrise, tranquil environment, Vietnam coastline, casting nets, morning light, silhouette, nature, fishing boat, serenity, ocean waves, sun reflections, local lifestyle, peaceful, crew members, traditional fishing, daily routine, candid moment, cultural heritage, photorealistic, documentary style, calm waters, fishing nets, golden hour, vivid colors, immersive atmosphere, natural scenery, rural life, community bonding, early morning, working class, local traditions, blue tones, soft shadows, persistence, deep connection, capturing motion, tranquil experience</v>
+        <v>vietnam student, education, studying late, apartment life, asian university, nighttime study, desk lamp glow, focused learning, academic concentration, urban apartment, young adult, notebooks scattered, textbook reading, casual attire, quiet surroundings, pensive expression, dim lighting, cozy atmosphere, documentary realism, natural lighting, study session, asian culture, authentic lifestyle, immersive storytelling, candid moment, everyday life, student life, home study, late-night focus, intellectual pursuit, academic dedication, quiet study time, reflective mood, apartment interior, cultural setting, relatable scene, lived-in space, domestic environment, realistic photography, emotional depth, human interaction, asian student, apartment details, real-world setting, warm lighting, snapshot moment</v>
       </c>
       <c r="D8" t="str">
-        <v>Local fishermen casting nets into the water at sunrise, surrounded by calm ocean waves and mist, embodying the serene beauty of Vietnam’s coastal lifestyle.</v>
+        <v>A Vietnamese student immersed in late-night studying in an urban apartment setting. The scene captures a candid moment of focused learning and academic dedication, enhanced by ambient lighting and authentic cultural details.</v>
       </c>
       <c r="E8" t="str">
-        <v>Landscapes</v>
+        <v>Lifestyle</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Young artists collaboratively painting vibrant murals on a street wall. The environment showcases a dynamic urban setting filled with color and creativity. Natural light falls onto the scene, highlighting their focused expressions as they engage passionately with their art. Captured with a Canon R5 camera, 35mm lens, at f/2. The composition emphasizes the collaboration and cultural impact of public art in a lively community setting.</v>
+        <v>Captured from a slightly elevated angle, the camera peers into the vibrant heart of a Vietnamese morning market, positioned at an eye-level that immerses the viewer into the candid hustle and bustle. The lens, likely a 35mm focal length, sharpens its focus on a middle-aged street vendor, whose movements are captured mid-cleanup as she wipes down her stall's counter. Her expression is focused, a natural testament to the daily rhythm of market life. The environment is richly layered, with bustling background activity slightly softened in focus, providing depth to the scene. Around her, other vendors and patrons create a tapestry of movement, some blurred by their swift passages, adding a dynamic energy to the frame. The light, a soft golden hue typical of early morning hours, warmly bathes the scene, casting gentle shadows that articulate the texture of worn concrete and the slight sheen on freshly washed surfaces. The framing is asymmetrical, naturally obstructed by hanging baskets and wayward market signage, adding to the documentary realism. This photograph captures the genuine, lived-in essence of a community steeped in its cultural and economic routines, ready for commercial licensing without a hint of artificiality.</v>
       </c>
       <c r="B9" t="str">
-        <v>Young Artists Painting Murals on Street Walls</v>
+        <v>Vietnamese Morning Market Cleanup</v>
       </c>
       <c r="C9" t="str">
-        <v>young artists, mural painting, creative environment, urban street, collaborative effort, vibrant colors, artistic expression, cultural relevance, community art, documentary style, public spaces, youth culture, graffiti, local neighborhood, mural project, inspiring creativity, colorful artwork, natural light, dynamic motion, hands-on activity, advertising for passion, artists at work, close collaboration, urban lifestyle, candid photography, innovative art, vibrancy, community bonding, textured walls, artistic tools, engagement, youth initiative, cultural dialogue, expressive art, neighborhood revitalization, collaboration, shared vision</v>
+        <v>vietnam market, street vendor, daily life, market cleanup, documentary realism, street scene, candid photography, morning activity, urban environment, human interaction, cultural experience, outdoor market, lifestyle photography, commercial potential, local vendors, community life, authentic observation, natural lighting, emotional authenticity, physical realism, layered perspectives, environmental storytelling, captured moment, human realism, bustling market, cultural immersion, people at work, honest emotion, real-life stories, vibrant street life, everyday routine, traditional culture, market stalls, handheld realism, urban texture, vivid details, spatial depth, environmental interaction, market dynamics, natural posture, vietnamese culture, communal space, photographic realism, visually immersive, professional quality, cultural narrative, commercial value</v>
       </c>
       <c r="D9" t="str">
-        <v>A group of young artists energetically paints colorful murals on street walls, contributing to the cultural vibrancy and creative landscape of their urban neighborhood in Vietnam.</v>
+        <v>An intimate and dynamic capture of a Vietnamese morning market as local vendors diligently engage in their daily cleanup tasks. The scene unfolds with authentic realism, layered with the rich textures and vibrant colors of a bustling market environment. Vendors are seen interacting naturally with their stalls and surroundings, embodying the essence of cultural and community life in Vietnam. The image is bathed in the soft, golden light of early morning, illuminating the movement and interactions among the people. The market environment is filled with the tactile details of wear and daily use, from the creased fabric of awnings to the humid glisten on metal surfaces. This photograph is not only a visual documentation of a specific cultural moment but also a commercial asset, capturing a genuine slice of life that resonates with viewers and effectively communicates an authentic human story.</v>
       </c>
       <c r="E9" t="str">
-        <v>Landscapes</v>
+        <v>Lifestyle</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>An elderly man animatedly sharing stories at a local café, seated comfortably with smiling companions. The intimate setting is enriched with natural light, emphasizing the warm atmosphere and connections between patrons. Shot with a Sony A7R IV using a 50mm lens at f/1.8, the composition captures candid moments of joy and cultural exchange in a charming neighborhood venue.</v>
+        <v>Position the camera at waist height, focusing closely on the aged, expressive hands of an elderly individual skillfully preparing ingredients in a traditional Vietnamese kitchen. The lens captures a narrow depth of field, ensuring the sharp focus remains on the hands, while the background softly blurs into the rich, textured environment, hinting at worn kitchen tools and local produce. The scene is lit by natural window light, creating a warm, diffuse glow that softly wraps around each element, adding a touch of nostalgia. The viewer should feel the tactile textures of the kitchen surfaces, the slight motion of the hands working rhythmically, and the ambient sounds of a lively cooking space. This observational angle gives a documentary feel, capturing the essence of culinary tradition and the emotional depth of a lived-in moment, inviting the audience into an intimate, culturally rich experience.</v>
       </c>
       <c r="B10" t="str">
-        <v>Elderly Man Sharing Stories at Local Café</v>
+        <v>Vietnamese Elderly Hands Cooking</v>
       </c>
       <c r="C10" t="str">
-        <v>elderly man, storytelling, local café, intimate environment, warm atmosphere, cultural exchange, community engagement, rich history, photorealistic, documentary style, sociability, traditional establishment, friendly interaction, candid photography, human connection, natural light, expressive gestures, i-contextual moments, community stories, cultural legacy, table setting, coffee cups, immersive experience, soft focus, endearing expressions, local culture, wholesome atmosphere, neighborhood charm, historical context, delightful conversation, aged wisdom, smiling faces, warm colors, relaxed vibe</v>
+        <v>vietnam cooking, elderly hands, food preparation, traditional kitchen, authentic lifestyle, culinary skills, cultural heritage, street food, vietnamese cuisine, local ingredients, preparing meal, home cooking, rustic kitchen, warm lighting, documentary realism, intimate atmosphere, culinary tradition, aging hands, family recipes, textured surfaces, natural light, kitchen interaction, emotionally grounded, candid moment, realism photography, food culture, cooking process, asian food, culinary art, street vendor, vietnamese culture, rich textures, kitchen tools, vintage kitchenware, culinary storytelling, daily life, human touch, traditional method, careful preparation, lived moment, handcrafted meal, kitchen scene, local lifestyle, immersive narrative, socio-cultural context, community tradition</v>
       </c>
       <c r="D10" t="str">
-        <v>An elderly man shares captivating stories with friends at a local café, fostering a sense of community in the warm and inviting atmosphere.</v>
+        <v>Capture a candid scene in a traditional Vietnamese kitchen. Focus on the hands of an elderly person engaged in the authentic preparation of a meal, capturing the cultural richness and culinary heritage. The environment is bustling with a warm, intimate atmosphere, highlighting the textures of local ingredients and aged kitchen tools. The moment feels natural and lived-in, emphasizing the physical interaction and emotional connection to the cooking process. The lighting is soft and diffused, casting gentle highlights that enhance the realism of the scene, making it feel as if it's part of a cherished memory.</v>
       </c>
       <c r="E10" t="str">
-        <v>Landscapes</v>
+        <v>Lifestyle</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>A couple riding a scooter through the scenic countryside, showcasing the adventure and joy of travel. The environment is lush and vibrant, with rolling hills and open skies all around. The scene is bathed in natural light, creating a sense of warmth and freedom. Shot with a Canon R5, 24mm lens at f/4. The composition highlights the connection between the couple and the surrounding beauty of Vietnam’s nature.</v>
+        <v>From a slight eye-level angle, capture a Vietnamese mechanic absorbed in repairing a scooter at a roadside garage during midday. The scene should reveal a bustling urban workshop, with the mechanic's hands delicately maneuvering around the scooter's engine. The composition uses an asymmetrical framing, placing the mechanic off-center to provide depth, showing other scooters and tools scattered. The lighting is natural, streaming gently from an open garage door, casting soft shadows and illuminating the mechanic's concentrated expression. A sense of motion is captured through slight blur from passing pedestrians, recreating the dynamic energy of the street. The focus prioritizes the mechanic and scooter, with the surrounding environment slightly softer, adding to the layered environmental depth. The candid, documentary-style image conveys a realistic snapshot of a day in the life of a Vietnamese urban mechanic, reflecting cultural authenticity through environmental interaction and human engagement.</v>
       </c>
       <c r="B11" t="str">
-        <v>Couple Riding a Scooter Through Scenic Countryside</v>
+        <v>Vietnamese Mechanic Repairing Scooter</v>
       </c>
       <c r="C11" t="str">
-        <v>couple, scooter, countryside, adventurous spirit, natural scenery, road trip, freedom, lush greenery, Vietnam landscape, joyful expression, intimate bond, dynamic movement, open road, sunny day, photorealistic, documentary style, happy moments, candid photography, travel lifestyle, exploration, tropical environment, cultural connection, sky background, road curves, lifestyle photography, emotional connection, adventure, vivid colors, shared experience, local culture, charming landscape, comfort, candid humor, speed, pageantry, natural light, sensation of freedom</v>
+        <v>vietnam mechanic, scooter repair, urban workshop, roadside garage, vietnam transportation, mechanic workshop, motorbike repair, street repair, vietnam culture, daily life, hands-on work, candid moment, authentic interaction, natural lighting, documentary style, work environment, busy street, local atmosphere, scooter maintenance, garage tools, mechanical work, craftsmanship, asian street, urban lifestyle, repair tools, bustling city, community interaction, vietnamese culture, real life scene, blue-collar work, roadside activity, human connection, scooter details, workbench, gritty textures, urban realism, lived-in space, hands-on activity, cultural authenticity, street photography, immersive scene, environmental storytelling, locally inspired, cultural snapshot, real-world interaction, everyday life</v>
       </c>
       <c r="D11" t="str">
-        <v>A couple joyfully rides a scooter through the picturesque Vietnamese countryside, embodying a sense of freedom and adventure amid lush landscapes.</v>
+        <v>A candid photograph capturing a Vietnamese mechanic deeply engaged in repairing a scooter at a bustling roadside garage. The scene unfolds with natural lighting, emphasizing the authenticity of urban street life in Vietnam. The mechanic's focused expression and interaction with the mechanical components encapsulate the vibrant culture and daily life of the local community.</v>
       </c>
       <c r="E11" t="str">
-        <v>Landscapes</v>
+        <v>Lifestyle</v>
       </c>
     </row>
   </sheetData>
